--- a/log.xlsx
+++ b/log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,6 +501,78 @@
       <c r="F3" t="inlineStr">
         <is>
           <t>c30b9280</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>TN 11 AI 9468</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-03-27 09:41:17</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Inside</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>6b6cd918</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>KA 02 ME 1140</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-03-27 09:47:44</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Inside</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0439752c</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>TN 07 CX 0580</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-03-27 09:57:06</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Inside</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>ba4c8a5f</t>
         </is>
       </c>
     </row>
